--- a/excel/kpi-trust-ledger_dashboard.xlsx
+++ b/excel/kpi-trust-ledger_dashboard.xlsx
@@ -281,6 +281,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_cert_chart'!$A$2:$A$7</f>
@@ -309,6 +310,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_cert_chart'!$A$2:$A$7</f>
@@ -334,6 +336,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -347,6 +350,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -399,6 +403,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_backlog'!$A$2:$A$5</f>
@@ -423,6 +428,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -451,6 +457,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -499,6 +506,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_source'!$A$2:$A$4</f>
@@ -523,6 +531,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -551,6 +560,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -599,6 +609,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_variance'!$A$2:$A$14</f>
@@ -624,6 +635,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -651,6 +663,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -699,6 +712,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_row_counts'!$A$2:$A$5</f>
@@ -723,6 +737,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -751,6 +766,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -900,6 +916,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_monthly'!$A$2:$A$7</f>
@@ -928,6 +945,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_monthly'!$A$2:$A$7</f>
@@ -952,6 +970,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -979,6 +998,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
